--- a/report/downloads/reports/网点变化对比报告_20261012_vs_20261019.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20261012_vs_20261019.xlsx
@@ -12286,7 +12286,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市慈溪市慈溪爱琴海</t>
+          <t>小米汽车浙江省宁波市镇海区镇海吾悦广场</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -12301,12 +12301,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>浙江省宁波市慈溪市新城大道北路和北三环东路交汇处爱琴海铺位号F1N009</t>
+          <t>浙江省宁波市镇海区望海南路与永茂西路交汇处镇海吾悦广场连廊处</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>连续在档 8 期</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -12318,7 +12318,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市镇海区镇海吾悦广场</t>
+          <t>小米汽车浙江省宁波市慈溪市慈溪爱琴海</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -12333,12 +12333,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>浙江省宁波市镇海区望海南路与永茂西路交汇处镇海吾悦广场连廊处</t>
+          <t>浙江省宁波市慈溪市新城大道北路和北三环东路交汇处爱琴海铺位号F1N009</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 8 期</t>
         </is>
       </c>
     </row>
@@ -13017,12 +13017,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州武进汽车城销售服务中心</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常州武进汽车城销售服务中心</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江苏省常州市武进区武进汽车城D区8号 → 江苏省常州市武进区湖塘镇武进汽车城D区8号</t>
+          <t>南通市开发区东方汽车城吉达路11号 → 江苏省南通市开发区吉达路11号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>小鹏汽车苏州东环路销售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>小鹏汽车苏州东环路销售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅 → 甘肃省兰州安宁区1757号</t>
+          <t>江苏省苏州市吴中区东兴路38号 → 江苏省苏州市吴中区吴东路1198号华星大楼</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
+          <t>开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨 → 开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>上海浦西保时捷中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>上海浦西保时捷中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江岸区黄浦科技园石桥一路10号 → 江岸区黄浦科技园石桥一路文博路口（公交站牌）</t>
+          <t>徐汇区徐虹中路21-25号3幢1层、2层202、203室 → 上海市徐汇区古宜路182号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>景德镇宝龙广场</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>景德镇宝龙广场</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江西省景德镇市昌南新区经一路宝龙广场M1-L1-034 → 江西省景德镇市昌南新区经一路宝龙广场1层M1-L1-004</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>潍坊乾宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>潍坊乾宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市青州市玲珑山北路3777号，262500 → 山东省潍坊市青州市玲珑山北路3777号</t>
+          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区黄河路与石港路交叉口路北</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>景德镇宝龙广场</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>景德镇宝龙广场</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 南庄镇樵乐路（吉利大道西）杜村工业区5号</t>
+          <t>江西省景德镇市昌南新区经一路宝龙广场M1-L1-034 → 江西省景德镇市昌南新区经一路宝龙广场1层M1-L1-004</t>
         </is>
       </c>
     </row>
@@ -13241,12 +13241,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>江岸区黄浦科技园石桥一路10号 → 江岸区黄浦科技园石桥一路文博路口（公交站牌）</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13288,29 +13288,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号 → 陕西省西安市浐灞生态区长鸣路以东南三环以北马腾空国际车城10113号</t>
+          <t>浙江省温州市乐清市康宁西路255号(南大产业园) → 浙江省温州市乐清市城南街道宁康西路255号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省黔西南布依族苗族自治州兴义市兴义汽车广场</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省黔西南布依族苗族自治州兴义市兴义汽车广场</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>贵州省兴义市桔山街道兴马大道与桔山B8路交汇处 → 黔西南州通源丰田汽车销售服务有限公司(兴马大道店)</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅 → 甘肃省兰州安宁区1757号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车苏州东环路销售展厅</t>
+          <t>潍坊乾宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车苏州东环路销售展厅</t>
+          <t>潍坊乾宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区东兴路38号 → 江苏省苏州市吴中区吴东路1198号华星大楼</t>
+          <t>山东省潍坊市青州市玲珑山北路3777号，262500 → 山东省潍坊市青州市玲珑山北路3777号</t>
         </is>
       </c>
     </row>
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小鹏汽车常州武进汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小鹏汽车常州武进汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13384,29 +13384,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区黄河路与石港路交叉口路北</t>
+          <t>江苏省常州市武进区武进汽车城D区8号 → 江苏省常州市武进区湖塘镇武进汽车城D区8号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>上海浦西保时捷中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>上海浦西保时捷中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>徐汇区徐虹中路21-25号3幢1层、2层202、203室 → 上海市徐汇区古宜路182号</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 南庄镇樵乐路（吉利大道西）杜村工业区5号</t>
         </is>
       </c>
     </row>
@@ -13428,17 +13428,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车随州鹿鹤大道销售服务中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车随州鹿鹤大道销售服务中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号1层 → 随州鹿鹤大道28号</t>
+          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
         </is>
       </c>
     </row>
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车随州鹿鹤大道销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车随州鹿鹤大道销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨 → 开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号1层 → 随州鹿鹤大道28号</t>
         </is>
       </c>
     </row>
@@ -13492,17 +13492,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13512,29 +13512,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市康宁西路255号(南大产业园) → 浙江省温州市乐清市城南街道宁康西路255号</t>
+          <t>西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号 → 陕西省西安市浐灞生态区长鸣路以东南三环以北马腾空国际车城10113号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>南通市开发区东方汽车城吉达路11号 → 江苏省南通市开发区吉达路11号</t>
+          <t>长安路与祥和大街交叉口 → 大杨庄村158号院内03号</t>
         </is>
       </c>
     </row>
@@ -13556,17 +13556,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车贵州省黔西南布依族苗族自治州兴义市兴义汽车广场</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车贵州省黔西南布依族苗族自治州兴义市兴义汽车广场</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>长安路与祥和大街交叉口 → 大杨庄村158号院内03号</t>
+          <t>贵州省兴义市桔山街道兴马大道与桔山B8路交汇处 → 黔西南州通源丰田汽车销售服务有限公司(兴马大道店)</t>
         </is>
       </c>
     </row>
@@ -13615,22 +13615,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Greater CN-CN-Chengdu Yintai IN99 Popup</t>
+          <t>小米汽车山东省聊城市东昌府区五洲汽车园</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小米汽车山东聊城市东昌府区五洲汽车园销售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13647,22 +13647,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省聊城市东昌府区五洲汽车园</t>
+          <t>Greater CN-CN-Maoming East Fun City Popup</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区五洲汽车园销售中心</t>
+          <t>茂名茂悦东荟城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13679,22 +13679,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省濮阳市华龙区中原西路</t>
+          <t>Greater CN-CN-Guiyang MixC One Popup</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市华龙区中原西路销售服务中心</t>
+          <t>贵阳万象汇</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13748,17 +13748,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Greater CN-CN-Guiyang MixC One Popup</t>
+          <t>Greater CN-CN-Chengdu Yintai IN99 Popup</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>贵阳万象汇</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13775,22 +13775,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Greater CN-CN-Maoming East Fun City Popup</t>
+          <t>小米汽车河南省濮阳市华龙区中原西路</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>茂名茂悦东荟城</t>
+          <t>小米汽车河南濮阳市华龙区中原西路销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13812,17 +13812,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江绍兴越城区苏宁广场汽车体验店专卖店</t>
+          <t>小米汽车山西大同市云冈区庞大汽车园</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
+          <t>小米汽车山西省大同市云冈区庞大汽车园销售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
@@ -13844,17 +13844,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云冈区庞大汽车园</t>
+          <t>小米之家浙江绍兴越城区苏宁广场汽车体验店专卖店</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省大同市云冈区庞大汽车园销售中心</t>
+          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
